--- a/levenshtein/levenshtein_sentences_toneless.xlsx
+++ b/levenshtein/levenshtein_sentences_toneless.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="1262">
   <si>
     <t>sentence_id</t>
   </si>
@@ -70,6 +70,24 @@
     <t>Wenzhou</t>
   </si>
   <si>
+    <t>Kunming</t>
+  </si>
+  <si>
+    <t>Pingyao</t>
+  </si>
+  <si>
+    <t>Shanghai</t>
+  </si>
+  <si>
+    <t>Lanzhou</t>
+  </si>
+  <si>
+    <t>Shantou</t>
+  </si>
+  <si>
+    <t>Tianjin</t>
+  </si>
+  <si>
     <t>ʂeiauoʂɻ̩lausan</t>
   </si>
   <si>
@@ -2819,6 +2837,969 @@
   </si>
   <si>
     <t>hekainaŋɲiseiafu</t>
+  </si>
+  <si>
+    <t>nɐkəoʂɻ̩lɔsɐ̃</t>
+  </si>
+  <si>
+    <t>lɔsɹ̩nætʰətsææikəpoŋiəutɕiɐ̃tʂəxuɐ</t>
+  </si>
+  <si>
+    <t>tʰəxæməuʂouɐ̃kæ</t>
+  </si>
+  <si>
+    <t>xæməutɐkʰætsætɕiɐ̃iɕiɔxɐtɕiəuuɐ̃lə</t>
+  </si>
+  <si>
+    <t>tʰəʂomɐʂɐ̃tsəutsɐkətʂɻ̩pɐ̃tʰiɛ̃ləxætsætɕiɐʂəu</t>
+  </si>
+  <si>
+    <t>nikʰənɐtiəokʰətʂʰə̃ʂəukʰə</t>
+  </si>
+  <si>
+    <t>tsænətiəputsætʂɻ̩tiə</t>
+  </si>
+  <si>
+    <t>pufɐ̃nətʂoŋtʂə̃iɔfɐ̃tʂɻ̩tʂoŋtʂə̃</t>
+  </si>
+  <si>
+    <t>tʰætoləpuɕiɔnətotʂɻ̩iɔtʂɻ̩ɕiɛtɕiəukəulə</t>
+  </si>
+  <si>
+    <t>tʂɻ̩kətɐnəkəxiɔtʂɻ̩liɐ̃kənɐkəxɔtiə</t>
+  </si>
+  <si>
+    <t>tʂɻ̩kəpinəkəxɔ</t>
+  </si>
+  <si>
+    <t>tʂɻ̩ɕiɛfɐ̃tsɹ̩məutənəɕiɛfɐ̃tsɹ̩xɔ</t>
+  </si>
+  <si>
+    <t>tʰətɕĩniɛ̃totɐlə</t>
+  </si>
+  <si>
+    <t>pʰɐiəusɐ̃ʂɻ̩tosueilɐ</t>
+  </si>
+  <si>
+    <t>tʂɻ̩kətoŋɕiiəutotʂoŋ</t>
+  </si>
+  <si>
+    <t>iəuuʂɻ̩tɕĩtsoŋ</t>
+  </si>
+  <si>
+    <t>kənɐtətoŋ</t>
+  </si>
+  <si>
+    <t>onɐtətoŋtʰənɐputoŋ</t>
+  </si>
+  <si>
+    <t>tʂə̃kənəputɕʰitʂoŋnəliɛ̃otunɐputoŋ</t>
+  </si>
+  <si>
+    <t>niʂonəxə̃xɔnixæxueiʂotiənɐiɐ̃</t>
+  </si>
+  <si>
+    <t>onətsueipə̃oʂopukotʰə</t>
+  </si>
+  <si>
+    <t>ʂoləipiɛ̃iəuʂoipiɛ̃</t>
+  </si>
+  <si>
+    <t>tɕʰĩnitɕiɛtsæʂoipiɛ̃</t>
+  </si>
+  <si>
+    <t>putsɔləkʰuætiəkʰə</t>
+  </si>
+  <si>
+    <t>tʂɻ̩xɐxætsɔnətə̃xɐtsækʰə</t>
+  </si>
+  <si>
+    <t>tʂʰɻ̩təfɐ̃tsækʰəkəiɔtə</t>
+  </si>
+  <si>
+    <t>mɐ̃tiətʂʰɻ̩mɐpuɕiɔtɕi</t>
+  </si>
+  <si>
+    <t>tsotətʂʰɻ̩pitʂɐ̃tətʂʰɻ̩xɔtiə</t>
+  </si>
+  <si>
+    <t>tʰətʂʰɻ̩təfɐ̃lənikətʂʰɻ̩tələ</t>
+  </si>
+  <si>
+    <t>tʰəkʰəkoʂɐ̃xæoməukʰəko</t>
+  </si>
+  <si>
+    <t>læuə̃uə̃tʂɻ̩toxuɐkəɕiɐ̃</t>
+  </si>
+  <si>
+    <t>kəoipə̃ʂu</t>
+  </si>
+  <si>
+    <t>otʂə̃kəməutənəpə̃ʂu</t>
+  </si>
+  <si>
+    <t>nikɔsoŋtʰə</t>
+  </si>
+  <si>
+    <t>xɔxɔnətsəumɔpʰɔ</t>
+  </si>
+  <si>
+    <t>ɕiɔɕĩkuɐ̃ɕiɐkʰəpʰɐpuʂɐ̃læ</t>
+  </si>
+  <si>
+    <t>isə̃tɕiɔnitoʂueiʂuei</t>
+  </si>
+  <si>
+    <t>tʂʰɻ̩iɛ̃tʂʰɻ̩tʂʰɐtuputʂuə̃</t>
+  </si>
+  <si>
+    <t>iɛ̃iɛxɔtʂʰɐiɛxɔotupuxixuɐ̃</t>
+  </si>
+  <si>
+    <t>pukuɐ̃nikʰəpukʰəfɐ̃tʂə̃̃otɔʂɻ̩iɔkʰənə</t>
+  </si>
+  <si>
+    <t>ofeikʰəpukʰo</t>
+  </si>
+  <si>
+    <t>niʂɻ̩nɐiniɛ̃lænə</t>
+  </si>
+  <si>
+    <t>oʂɻ̩tɕʰiɛ̃niɛ̃tɔpətɕĩnə</t>
+  </si>
+  <si>
+    <t>tɕiəʐɻ̩kʰæxueinɐkətɐ̃tʂuɕi</t>
+  </si>
+  <si>
+    <t>niiɔtɕʰĩonəkʰələ</t>
+  </si>
+  <si>
+    <t>imiɛ̃tsəuimiɛ̃tɕiɐ̃</t>
+  </si>
+  <si>
+    <t>iɛtsəuiɛiɛ̃iɛʂoiɛto</t>
+  </si>
+  <si>
+    <t>ænəkətoŋɕinɐkəo</t>
+  </si>
+  <si>
+    <t>iəuɕiɛtifɐ̃̃ætʰæiɐ̃tɕiɔʐətʰəu</t>
+  </si>
+  <si>
+    <t>nikueiɕĩoɕĩuɐ̃</t>
+  </si>
+  <si>
+    <t>niɕĩuɐ̃oiɛɕĩuɐ̃omə̃liɐ̃kətuɕĩuɐ̃</t>
+  </si>
+  <si>
+    <t>nitɕʰiɛ̃kʰəmɐomə̃tə̃ixɐtsækʰə</t>
+  </si>
+  <si>
+    <t>nikətsɐiɛ̃</t>
+  </si>
+  <si>
+    <t>nikəʐə̃tənəkəʐə̃</t>
+  </si>
+  <si>
+    <t>sueiliʌʔŋiɤsɹ̩lɔsɑŋ</t>
+  </si>
+  <si>
+    <t>lɔsɹ̩liʌʔuʌʔtɕiɑtʂɻ̩xuxuæpʰəŋiəutɔɕiʌʔliʌʔ</t>
+  </si>
+  <si>
+    <t>uʌʔtɕiɑxɑŋmʌʔlɑsuʌʔuɑŋliʌʔ</t>
+  </si>
+  <si>
+    <t>mɑliʌʔxɑŋtiʌʔtʂəŋtʂəŋ</t>
+  </si>
+  <si>
+    <t>uʌʔtɕiɑsuʌʔtsʰəutsɥtɕiəutsəutsɑtitsʌʔiŋtsɑŋxuɑŋxɑŋtsætɕyɤʂɻ̩ɤliʌʔ</t>
+  </si>
+  <si>
+    <t>n̩tɔlɑʐʌʔtiʌʔlæŋiɤtɔtʂʰəŋxʌʔleitiʌʔlæ</t>
+  </si>
+  <si>
+    <t>tsæuæʐʌʔpʌʔtsætsæʐʌʔ</t>
+  </si>
+  <si>
+    <t>pʌʔsɹ̩uʌʔtixuætsuʌʔiɔtsʌʔtixuætsuʌʔ</t>
+  </si>
+  <si>
+    <t>tʰæteilɑyŋpʌʔtsuʌʔuʌʔɕiɤɕiɤtsʌʔɕiɤɕiɤtɕiəuɕiɑliɑ</t>
+  </si>
+  <si>
+    <t>tsʌʔxuæteiuʌʔxuæɕiɔtsʌʔliɑŋxuælɑiʌʔxuæxɔɕiɤʐʌʔliʌʔ</t>
+  </si>
+  <si>
+    <t>tsʌʔxuæpiuʌʔxuæxɔ</t>
+  </si>
+  <si>
+    <t>tsʌʔɕiɤʐʌʔxuətsʌʔpʌʔtiuʌʔɕiɤʐʌʔxuətsʌʔxɔ</t>
+  </si>
+  <si>
+    <t>uʌʔtɕiɑtɕiŋɲiɤteiʂɔɲiɤtɕiliɑ</t>
+  </si>
+  <si>
+    <t>yʌʔmʌʔiəusɑŋʂʌʔlæsueiuɑ</t>
+  </si>
+  <si>
+    <t>tsʌʔxuætuŋseiiəuteilætsuŋliʌʔ</t>
+  </si>
+  <si>
+    <t>iəuuʌʔʂʌʔtɕiŋtsuŋliʌʔ</t>
+  </si>
+  <si>
+    <t>xeituŋlɔ</t>
+  </si>
+  <si>
+    <t>ŋiɤxeituŋlɔuʌʔtɕiɑxeipʌʔtuŋ</t>
+  </si>
+  <si>
+    <t>pʌʔtɕʰiŋliʌʔliɤŋiɤiɤxeipʌʔtuŋ</t>
+  </si>
+  <si>
+    <t>n̩suʌʔtiʌʔpʌʔlæn̩xɑŋxuæsuʌʔɕiɤʐʌʔʂəŋliʌʔ</t>
+  </si>
+  <si>
+    <t>ŋiɤtsueipəŋŋiɤsuʌʔpʌʔkueiuʌʔtɕiɑtiʌʔ</t>
+  </si>
+  <si>
+    <t>suʌʔlɔiʌʔpiɤiəusuʌʔiʌʔpiɤ</t>
+  </si>
+  <si>
+    <t>tɕʰiŋn̩tsæsuʌʔiʌʔpiɤ</t>
+  </si>
+  <si>
+    <t>pʌʔtsɔlɑkʰuæɕiɤʐʌʔtɕʰyuɑ</t>
+  </si>
+  <si>
+    <t>tsʌʔtʂəŋtʂəŋxɑŋtsɔliʌʔtəŋtʂəŋtʂəŋtsætɕʰyuɑ</t>
+  </si>
+  <si>
+    <t>tʂʰʌʔlɔxuɑŋtsætɕʰyɕiɑpʌʔɕiɑ</t>
+  </si>
+  <si>
+    <t>mɑŋɕiɤʐʔtʂʰʌʔpʌʔyŋtʂɔtɕiʌʔ</t>
+  </si>
+  <si>
+    <t>tɕyɤtiʌʔtʂʰʌʔpitsɑŋtiʌʔtʂʰʌʔxɔɕiɤʐʌʔ</t>
+  </si>
+  <si>
+    <t>uʌʔtɕiɑtʂʰʌʔlɔxuɑŋlɑn̩tʂʰʌʔlɔxuɑŋlɑmʌʔlɑ</t>
+  </si>
+  <si>
+    <t>uʌʔtɕiɑtɕʰykueiʂɑŋxæŋiɤmʌʔlɑtɕʰykuei</t>
+  </si>
+  <si>
+    <t>n̩læuŋuŋtsʌʔtueixuɑɕiɑŋpʌʔɕiɑŋ</t>
+  </si>
+  <si>
+    <t>tɕyŋiɤiʌʔpəŋsɥ</t>
+  </si>
+  <si>
+    <t>ŋiɤtʂəŋtiʌʔmʌʔlɑuʌʔpəŋsɥ</t>
+  </si>
+  <si>
+    <t>n̩kɔtɕyuʌʔtɕiɑ</t>
+  </si>
+  <si>
+    <t>xɔxɔtitsəupʌʔyŋpʰɔ</t>
+  </si>
+  <si>
+    <t>ɕiɔɕiŋtiʌʔxɑtiʌʔpɑpʌʔsuəlæ</t>
+  </si>
+  <si>
+    <t>isəŋtɕiɔn̩teisueisuei</t>
+  </si>
+  <si>
+    <t>tʂʰʌʔiɤxʌʔtsʰɑtupʌʔɕiɑ</t>
+  </si>
+  <si>
+    <t>iɤiɤxɔtsʰɑiɤxɔŋiɤteipʌʔxɔ</t>
+  </si>
+  <si>
+    <t>pʌʔkuɑŋn̩tɕʰypʌʔtɕʰyxuɑŋtʂəŋŋiɤsɹ̩iɔtɕʰyliʌʔ</t>
+  </si>
+  <si>
+    <t>ŋiɤxueitɕʰypʌʔɕiɑ</t>
+  </si>
+  <si>
+    <t>n̩sɹ̩lɑɲiɤlætiʌʔliʌʔ</t>
+  </si>
+  <si>
+    <t>ŋiɤsɹ̩tɕiɤɲiɤtɔtiʌʔpiʌʔtɕiŋ</t>
+  </si>
+  <si>
+    <t>tɕiŋʐʌʔkʰæxuæsueitiʌʔtsɥɕiʌʔ</t>
+  </si>
+  <si>
+    <t>n̩tiʌʔtɕʰiŋtɕʰiŋŋiɤ</t>
+  </si>
+  <si>
+    <t>iʌʔpiɤtsəuiʌʔpiɤsuʌʔ</t>
+  </si>
+  <si>
+    <t>yʌʔtsəuyʌʔyɤyʌʔsuʌʔyʌʔtei</t>
+  </si>
+  <si>
+    <t>pɑuʌʔxuætuŋseitɕyŋiɤxeikueilæ</t>
+  </si>
+  <si>
+    <t>iəuɕiɤtixuəxuəpɑtʰæiɑŋxuɑŋʐʌʔtəuiɤ</t>
+  </si>
+  <si>
+    <t>n̩ɕiŋʂəŋliʌʔŋiɤɕiŋuə</t>
+  </si>
+  <si>
+    <t>n̩ɕiŋuəŋiɤiɤɕiŋuətsɑliɑŋxuæʐəŋteiɕiŋuə</t>
+  </si>
+  <si>
+    <t>n̩ɕiɤtɕʰyuɑŋʌʔməŋtəŋtəŋtsætɕʰy</t>
+  </si>
+  <si>
+    <t>n̩tʂʰʌʔpʌʔtʂʰʌʔiɤ</t>
+  </si>
+  <si>
+    <t>n̩ʐəŋtiʌʔuʌʔxuæʐəŋpʌʔʐəŋtiʌʔ</t>
+  </si>
+  <si>
+    <t>saɲiŋŋuzɹ̩aʔse</t>
+  </si>
+  <si>
+    <t>sɹ̩neitsəŋlaʔhetaʔiɪʔɦəʔbɑ̃ɦiɤkɑ̃ɦeɦo</t>
+  </si>
+  <si>
+    <t>ɦiɦɛɦm̩məʔkɑ̃hɔɦa</t>
+  </si>
+  <si>
+    <t>ɦɛɦm̩məʔdaketsekɑ̃iɪʔɕiɪʔʑiɤkɑ̃hɔləʔ</t>
+  </si>
+  <si>
+    <t>ɦikɑ̃mozɑ̃ʑiɤtsɤnanəŋkaɕyduzəŋkuɑ̃ɦɛlaʔlaʔoliɕiã</t>
+  </si>
+  <si>
+    <t>noŋtɔsadifɑ̃tɕʰiŋotɔzɑ̃hetɕʰi</t>
+  </si>
+  <si>
+    <t>laʔɛmivəʔlaʔgəʔtaʔ</t>
+  </si>
+  <si>
+    <t>vəʔiɔɛnəŋtsuzɹ̩iɔgəʔnəŋkatsu</t>
+  </si>
+  <si>
+    <t>tʰəʔduləʔvəʔiɔkaɕydutsəʔiɔgəʔtiʑiɤkɤləʔ</t>
+  </si>
+  <si>
+    <t>gəʔtsaʔduetsaʔɕiauliãtsaʔliɕiãɦaliiɪʔtsãʔhɔiɪʔŋene</t>
+  </si>
+  <si>
+    <t>diɪʔɦəʔpiɛɦəʔhɔ</t>
+  </si>
+  <si>
+    <t>diɪʔŋevɑ̃tsɹ̩piimiiɪʔŋevãtsɹ̩tʰepe</t>
+  </si>
+  <si>
+    <t>ɦitɕiŋɲitɕisøləʔ</t>
+  </si>
+  <si>
+    <t>daiaʔsesəʔsøɦuãlivaʔ</t>
+  </si>
+  <si>
+    <t>gəʔtsaʔɦməʔzɹ̩ɦiɤtɕihozoŋ</t>
+  </si>
+  <si>
+    <t>ɦiɤtəʔŋ̩səʔtɕiŋzoŋ</t>
+  </si>
+  <si>
+    <t>netəʔdoŋvaʔ</t>
+  </si>
+  <si>
+    <t>ŋonetəʔdoŋɦinevəʔdoŋ</t>
+  </si>
+  <si>
+    <t>tsəŋvəʔtɕʰiŋzoŋtəʔleliŋoɦɑnevəʔdoŋ</t>
+  </si>
+  <si>
+    <t>noŋkɑ̃təʔlɔhɔɦənoŋɦɛɦuekɑ̃tisanə</t>
+  </si>
+  <si>
+    <t>ɦokɑ̃vəʔdaleŋokɑ̃vəʔkuɦi</t>
+  </si>
+  <si>
+    <t>kɑ̃ləʔiɪʔpiɦiɤkãiɪʔpi</t>
+  </si>
+  <si>
+    <t>tɕʰiŋnoŋtsekɑ̃iɪʔpi</t>
+  </si>
+  <si>
+    <t>vəʔtsɔləʔɦɔsɔtɕʰivaʔ</t>
+  </si>
+  <si>
+    <t>ɦizeɦɛtsɔlaʔhekutʰəʔiɪʔɕiɪʔtsetɕʰihɸle</t>
+  </si>
+  <si>
+    <t>tɕʰiɪʔləʔvetsetɕinanəŋ</t>
+  </si>
+  <si>
+    <t>memetɕiɔtɕiɪʔvəʔiɔtɕiɪʔ</t>
+  </si>
+  <si>
+    <t>zulaʔhetɕʰiɪʔpililaʔhetɕʰiɪʔhɔiɪʔŋe</t>
+  </si>
+  <si>
+    <t>ɦivetɕʰiɪʔkuləʔnoŋvetɕʰiɪʔkuvaʔ</t>
+  </si>
+  <si>
+    <t>ɦizɑ̃hetɕʰikuləʔŋoɦm̩məʔtɕʰiku</t>
+  </si>
+  <si>
+    <t>leməŋməŋkʰøgəʔtuhoɕiãvaʔ</t>
+  </si>
+  <si>
+    <t>pəʔŋoiɪʔpəŋsɹ̩</t>
+  </si>
+  <si>
+    <t>ŋotsəŋɦəɦm̩məʔsɹ̩</t>
+  </si>
+  <si>
+    <t>noŋtʰəʔɦikɑ̃</t>
+  </si>
+  <si>
+    <t>ɦɔɦɔtɕiɔtsɤvəʔiɔpəŋ</t>
+  </si>
+  <si>
+    <t>tɑ̃ɕiŋgueɦotɕʰiboɦabovəʔzɑ̃le</t>
+  </si>
+  <si>
+    <t>isãtɕiɔnoŋtukuəŋkuəŋ</t>
+  </si>
+  <si>
+    <t>tɕʰiɪʔɕiãitɕʰiɪʔzozevəʔhɔɦə</t>
+  </si>
+  <si>
+    <t>ilɔzolɔŋozevəʔhuøɕi</t>
+  </si>
+  <si>
+    <t>vəʔkuønoŋtɕʰivəʔtɕʰifetsəŋŋozɹ̩iɔtɕʰiɦə</t>
+  </si>
+  <si>
+    <t>ŋozɹ̩iɪʔdiŋiɔtɕʰiɦəʔ</t>
+  </si>
+  <si>
+    <t>noŋzɹ̩ɦaliiɪʔɲileɦəʔ</t>
+  </si>
+  <si>
+    <t>ŋozɹ̩ʑiɲitɔpoʔtɕiŋɦəʔ</t>
+  </si>
+  <si>
+    <t>tɕiuŋtsɔkʰeɦuesaɲiŋtsutsɹ̩ʑiɪʔ</t>
+  </si>
+  <si>
+    <t>noŋiɔtɕʰiŋŋotɕʰiɪʔvegəʔ</t>
+  </si>
+  <si>
+    <t>iɪʔmitsɤiɪʔmikɑ̃</t>
+  </si>
+  <si>
+    <t>ɦyɪʔtsɤɦyɪʔɦypɦyɪʔkɑ̃ɦyɪʔtu</t>
+  </si>
+  <si>
+    <t>neimigəʔməʔzɹ̩pəʔŋo</t>
+  </si>
+  <si>
+    <t>ɦiɤtsoŋdifɑ̃netʰaɦiãtɕiɔɲiɪʔdɤ</t>
+  </si>
+  <si>
+    <t>noŋkueɕiŋŋoɕiŋɦuɑ̃</t>
+  </si>
+  <si>
+    <t>noŋɕiŋɦuɑ̃ŋoɦaɕiŋɦuɑ̃aʔlaliãkadɤzeɕiŋɦuɑ̃</t>
+  </si>
+  <si>
+    <t>noŋɕitɕʰivaʔaʔlatəŋtʰəʔiɪʔɕiɪʔtsetɕʰi</t>
+  </si>
+  <si>
+    <t>noŋɕiãitɕʰiɪʔvaʔ</t>
+  </si>
+  <si>
+    <t>noŋɲiŋtəʔemiɦəʔɲiŋvaʔ</t>
+  </si>
+  <si>
+    <t>feiʂavəʂɻ̩lɔsɛ̃n</t>
+  </si>
+  <si>
+    <t>lɔʂɻ̩lɛtʰatʂə̃nliɛ̃nikəpə̃nioufəxuatʂəli</t>
+  </si>
+  <si>
+    <t>tʰaxɛ̃nm̩ioufəpama</t>
+  </si>
+  <si>
+    <t>xɛ̃nm̩iouxapaxɛ̃ntəixueiɯtɕioufəvɛ̃nlɔ</t>
+  </si>
+  <si>
+    <t>tʰafəmaʂɑ̃tɕioutsoulitʂɻ̩mə̃npɛ̃tʰiɛ̃nlɔtsə̃nməxɛ̃ntsɛvuliliʂa</t>
+  </si>
+  <si>
+    <t>ɲilalitɕʰilivətɕĩntʂʰə̃ntɕʰili</t>
+  </si>
+  <si>
+    <t>tsɛlɛtalim̩ioutsɜtʂɻ̩ta</t>
+  </si>
+  <si>
+    <t>puʂɻ̩lɛmə̃ntikətsufatʂɻ̩mə̃ntsutʂəli</t>
+  </si>
+  <si>
+    <t>tʰɛtuəlɔỹnpuʂɑ̃lɛmə̃nɕiətsɹ̩tsɻ̩mə̃nɕiətɕioukoulɔ</t>
+  </si>
+  <si>
+    <t>tʂɻ̩kətalɛkəkatʂɻ̩liɑ̃kəlakəxɔɕiəʂa</t>
+  </si>
+  <si>
+    <t>tʂɻ̩kəkɛ̃nlɛkəxɔmɛ̃n</t>
+  </si>
+  <si>
+    <t>tʂɻ̩ɕiəfɑ̃tsɹ̩m̩ioulɛɕiəfɑ̃tsɹ̩xɔ</t>
+  </si>
+  <si>
+    <t>tʰatɕĩnɲiɛ̃ntuətalɔ</t>
+  </si>
+  <si>
+    <t>tamuɯsɛ̃nʂɻ̩tuəlɔ</t>
+  </si>
+  <si>
+    <t>tʂɻ̩kətũnɕiioutuəpfə̃nʂa</t>
+  </si>
+  <si>
+    <t>xapaiouvuʂɻ̩lɛtɕĩnli</t>
+  </si>
+  <si>
+    <t>lə̃nlatũnma</t>
+  </si>
+  <si>
+    <t>vələ̃nlatũntʰalaputũn</t>
+  </si>
+  <si>
+    <t>aʂɻ̩xuaputɕʰĩnlaliɛ̃nvətoulaputũnla</t>
+  </si>
+  <si>
+    <t>ɲifətixɔuaɲixɛ̃nxueifəɕiəsaʂa</t>
+  </si>
+  <si>
+    <t>vətitsueipə̃ntixə̃nvəfəpukuəla</t>
+  </si>
+  <si>
+    <t>fəlɔitʂʰɛ̃nkəioufəlɔitʂʰɛ̃n</t>
+  </si>
+  <si>
+    <t>tɕiatɕʰĩnɲitsʰũnfəitʂʰɛ̃n</t>
+  </si>
+  <si>
+    <t>putsɔlɔkʰuɛɕiətɕʰiʂa</t>
+  </si>
+  <si>
+    <t>tɕiaxɛ̃ntsɔtʂəlitə̃nixalɔtsɛtɕʰiʂa</t>
+  </si>
+  <si>
+    <t>tʂʰɻ̩pafɛ̃nlɔtsɛtɕʰipfə̃nlipu</t>
+  </si>
+  <si>
+    <t>tɕiamɛ̃nɕiətʂʰɻ̩ʂapulɔtɕi</t>
+  </si>
+  <si>
+    <t>tsuəxalɔtʂʰɻ̩pitʂɛ̃ntʂətʂʰɻ̩xɔɕiəɯ</t>
+  </si>
+  <si>
+    <t>tʰatʂʰɻ̩lɔfɛ̃nlɔɲitʂʰɻ̩lɔm̩iou</t>
+  </si>
+  <si>
+    <t>latsouluəʂɑ̃xɛvəm̩ioutɕʰikuə</t>
+  </si>
+  <si>
+    <t>tɕiaɲivə̃nkɯxatʂɻ̩kəxuaɯɕiɑ̃puɕiɑ̃</t>
+  </si>
+  <si>
+    <t>kɯvəkɯipə̃nfu</t>
+  </si>
+  <si>
+    <t>vəʂɻ̩xuam̩ioufu</t>
+  </si>
+  <si>
+    <t>ɲikɯlafəixa</t>
+  </si>
+  <si>
+    <t>tɕiaxɔxɔtitsoupulɔpʰɔlɔʂa</t>
+  </si>
+  <si>
+    <t>ɕiɔɕĩntiəxatɕʰiʂɑ̃pulɛ</t>
+  </si>
+  <si>
+    <t>iʂə̃ntɕiɔɲituəfeiiɯli</t>
+  </si>
+  <si>
+    <t>tʂʰouiɛ̃nxətʂʰatoupupfə̃n</t>
+  </si>
+  <si>
+    <t>iɛ̃niəpatʂʰaiəpavətoupuɛ</t>
+  </si>
+  <si>
+    <t>pukuɛ̃nɲitɕʰiputɕʰifɛ̃ntʂə̃nvəiɔtɕʰili</t>
+  </si>
+  <si>
+    <t>tsə̃nməxalɔvətouiɔtɕʰili</t>
+  </si>
+  <si>
+    <t>tɕiaɲiʂɻ̩laiɲiɛ̃nlɛtiʂa</t>
+  </si>
+  <si>
+    <t>vəʂɻ̩tɕʰiɛ̃nɲiɛ̃nkətɔpətɕĩnti</t>
+  </si>
+  <si>
+    <t>tɕĩnkətʰiɛ̃nkʰɛxueifeiʂɻ̩pfuɕiʂa</t>
+  </si>
+  <si>
+    <t>tɕiaɲiiɔpavətɕʰĩnixali</t>
+  </si>
+  <si>
+    <t>imiɛ̃ntsoutʂəliimiɛ̃nfətʂəli</t>
+  </si>
+  <si>
+    <t>yətsouyəyɛ̃nlɔyəfəyətuəlɔ</t>
+  </si>
+  <si>
+    <t>tɕiapalɛkətũnɕikɯvətɕʰykɯixaʂa</t>
+  </si>
+  <si>
+    <t>iouɕiətifɑ̃patʰɛiɑ̃tɕiɔʐɻ̩tʰou</t>
+  </si>
+  <si>
+    <t>ɲiɕinsavəɕĩnvɑ̃</t>
+  </si>
+  <si>
+    <t>ɲiɕĩnvɑ̃vəiəɕĩnvɑ̃vəmə̃nliɑ̃kəʐə̃ntouɕĩnvɑ̃</t>
+  </si>
+  <si>
+    <t>ɲiɕiɛ̃ntɕʰiʂavəmə̃ntə̃nixalɔtsɛtɕʰi</t>
+  </si>
+  <si>
+    <t>iɛ̃nɲitʂʰoulimaputʂʰou</t>
+  </si>
+  <si>
+    <t>lɛkəʐə̃nɲiʐə̃ntəʐə̃nputə</t>
+  </si>
+  <si>
+    <t>titiaŋuakaiaalusã</t>
+  </si>
+  <si>
+    <t>alausinẽitsiãkaʔkaipʰeŋiulotãue</t>
+  </si>
+  <si>
+    <t>ihuãtãbueliaua</t>
+  </si>
+  <si>
+    <t>huãbuetsʰamtokeʔkekʰuŋkiãtsiutãtik</t>
+  </si>
+  <si>
+    <t>itãtsiaksitsiukiãtsonĩkaukuahuãtolai</t>
+  </si>
+  <si>
+    <t>lɯãikʰɯtikouaãilaikʰɯsiãlai</t>
+  </si>
+  <si>
+    <t>tohɯkobototsiko</t>
+  </si>
+  <si>
+    <t>mmĩhĩhẽtsotioʔtsĩsẽtso</t>
+  </si>
+  <si>
+    <t>kʰaʔtsoioumiaŋhiõtsoitsiõtsoitsiulaou</t>
+  </si>
+  <si>
+    <t>tsikaituahɯkaisoitsinõkaimuẽʔtikaioiiauhonẽ</t>
+  </si>
+  <si>
+    <t>tsikaihokuehɯkai</t>
+  </si>
+  <si>
+    <t>tsitsʰoʔtsʰubohɯtsʰoʔtsʰuho</t>
+  </si>
+  <si>
+    <t>ikimnĩzioʔtsoihueou</t>
+  </si>
+  <si>
+    <t>tsʰamtosãtsapguahuenõ</t>
+  </si>
+  <si>
+    <t>tsikaimuẽʔuzioʔtaŋa</t>
+  </si>
+  <si>
+    <t>hiatioʔuŋõutsapkɯŋtaŋnõ</t>
+  </si>
+  <si>
+    <t>kʰioʔoitiŋtaŋboi</t>
+  </si>
+  <si>
+    <t>uakʰioʔoitiŋtaŋikʰioʔmtiŋtaŋ</t>
+  </si>
+  <si>
+    <t>bohokʰiŋtaŋkauualokʰioʔmtiŋtaŋa</t>
+  </si>
+  <si>
+    <t>lɯtãlaihoʔholɯluãupiaŋtãkekomĩʔkaibo</t>
+  </si>
+  <si>
+    <t>uaboitãueuatãsui</t>
+  </si>
+  <si>
+    <t>tãtsekkueliauiutãkekue</t>
+  </si>
+  <si>
+    <t>taʰiãlɯtãkekue</t>
+  </si>
+  <si>
+    <t>bohotsaoumẽmẽkʰɯ</t>
+  </si>
+  <si>
+    <t>tsitsuŋhuãtsatotaŋetsiãlaikʰɯ</t>
+  </si>
+  <si>
+    <t>tsiaʔpatsiãlaikʰɯkʰaʔho</t>
+  </si>
+  <si>
+    <t>kʰuãnĩtsiaʔmãikiŋtsiaŋ</t>
+  </si>
+  <si>
+    <t>tsopaŋkotsiaʔhokuekʰiapaŋkotsiaʔ</t>
+  </si>
+  <si>
+    <t>itsiaʔhooulɯtsiaʔhobue</t>
+  </si>
+  <si>
+    <t>ikʰɯkuesiaŋhaiuabokʰɯkue</t>
+  </si>
+  <si>
+    <t>laipʰĩtʰõitsipʰauhuekʰaʔoipʰaŋ</t>
+  </si>
+  <si>
+    <t>kʰioʔpuŋtsɯkʰɯʔua</t>
+  </si>
+  <si>
+    <t>uatsiŋsikbohɯpuŋtsɯli</t>
+  </si>
+  <si>
+    <t>lɯkaʔitã</t>
+  </si>
+  <si>
+    <t>kiãhomãitsau</t>
+  </si>
+  <si>
+    <t>tsaikuaŋmãipuaʔkʰɯliaupeʔmtikkʰia</t>
+  </si>
+  <si>
+    <t>uiseŋkiolɯĩʔtsoie</t>
+  </si>
+  <si>
+    <t>tsiaʔhuŋasitsiaʔteloŋmõ</t>
+  </si>
+  <si>
+    <t>huŋahoteahoualoŋboiŋiaŋ</t>
+  </si>
+  <si>
+    <t>talilɯkʰɯamualitsiãtoãikʰɯ</t>
+  </si>
+  <si>
+    <t>uaŋẽhõuãikʰɯ</t>
+  </si>
+  <si>
+    <t>lɯkaititseknĩlaikai</t>
+  </si>
+  <si>
+    <t>uasitsõinĩlaipakkiãkai</t>
+  </si>
+  <si>
+    <t>kimzikkʰuihuetitiaŋtsotsutsʰioʔ</t>
+  </si>
+  <si>
+    <t>lɯtioʔtsʰiãua</t>
+  </si>
+  <si>
+    <t>tsʰiaukiãtsʰiautã</t>
+  </si>
+  <si>
+    <t>zukiãzuhŋzutãzutsoi</t>
+  </si>
+  <si>
+    <t>hɯkaimuẽʔkʰioʔpuŋua</t>
+  </si>
+  <si>
+    <t>ulaŋlotihŋliaʔtsiatʰaiiaŋkiotsoziktʰau</t>
+  </si>
+  <si>
+    <t>lɯkuisẽuasẽheŋ</t>
+  </si>
+  <si>
+    <t>lɯsẽheŋuaasẽheŋnaŋnõnaŋloŋsẽheŋ</t>
+  </si>
+  <si>
+    <t>lɯsõikʰɯuaŋtaŋetsiãlaikʰɯ</t>
+  </si>
+  <si>
+    <t>lɯkʰaʔutsiaʔhuŋ</t>
+  </si>
+  <si>
+    <t>lɯkʰaʔoipakhɯkaimuẽʔ</t>
+  </si>
+  <si>
+    <t>seiiɑuosɹ̩lɑusan</t>
+  </si>
+  <si>
+    <t>lɑusɹ̩nətʰɑtʂəŋkənikəpʰəŋiouʂuotʂəxuɑnə</t>
+  </si>
+  <si>
+    <t>tʰɑxaimeiʂuovanmɑ</t>
+  </si>
+  <si>
+    <t>xaimeiioutɑkaitsaitaixuərtɕiouʂuovanlə</t>
+  </si>
+  <si>
+    <t>tʰɑsuomɑsɑŋtɕioutsounənmənənməpantʰianləxaitaitɕiɑli</t>
+  </si>
+  <si>
+    <t>niʂɑŋnɑxərtɕʰyuoʂaŋtʂʰəŋlitɕʰy</t>
+  </si>
+  <si>
+    <t>tainɑxərputaitɕiexər</t>
+  </si>
+  <si>
+    <t>pusɹ̩nɑmətsuosɹ̩tsənmətsuo</t>
+  </si>
+  <si>
+    <t>tʰaituoləʐuŋpuliɑunɑmətuotɕiouiɑutsənmətuotɕiouhoulə</t>
+  </si>
+  <si>
+    <t>tseikətɑneikəɕiɑutseiliɑneikəxɑuitiarnə</t>
+  </si>
+  <si>
+    <t>tseikəpineikəxɑu</t>
+  </si>
+  <si>
+    <t>tɕieɕiefɑŋtsɹ̩puyneiɕiefɑŋtsɹ̩xɑu</t>
+  </si>
+  <si>
+    <t>tʰɑtɕinniantuotɑlə</t>
+  </si>
+  <si>
+    <t>tɑkaitɕʰisanʂɻ̩laisuərpɑ</t>
+  </si>
+  <si>
+    <t>tseikətuŋɕiioutuotsuŋnə</t>
+  </si>
+  <si>
+    <t>iouuʂɻ̩tɕintsuŋnə</t>
+  </si>
+  <si>
+    <t>nɑtituŋmɑ</t>
+  </si>
+  <si>
+    <t>uonɑtituŋtʰɑnɑputuŋ</t>
+  </si>
+  <si>
+    <t>tsənputɕʰiŋsəŋtsuŋtiuotounɑputuŋ</t>
+  </si>
+  <si>
+    <t>niʂuotitʂənxɑunixaixueiʂuotiarmɑiɑ</t>
+  </si>
+  <si>
+    <t>uotsueipənuoʂuopukuotʰɑ</t>
+  </si>
+  <si>
+    <t>tɕʰiŋnitaiʂuoipian</t>
+  </si>
+  <si>
+    <t>putsɑuləkʰuaitɕʰypɑ</t>
+  </si>
+  <si>
+    <t>ɕiantsaixaitsɑutʂənətəŋxuərtaitɕʰypɑ</t>
+  </si>
+  <si>
+    <t>tʂʰɻ̩vanfantaitɕʰyxɑumɑ</t>
+  </si>
+  <si>
+    <t>marmartʂʰɻ̩pɑpietʂɑutɕi</t>
+  </si>
+  <si>
+    <t>tsuotʂətʂʰɻ̩pitsantʂətʂʰɻ̩xɑu</t>
+  </si>
+  <si>
+    <t>tʰɑtʂʰɻ̩vanfanlənitʂʰɻ̩fanləmeiiou</t>
+  </si>
+  <si>
+    <t>tʰɑtɕʰykuoʂɑŋxaiuomeitɕʰykuo</t>
+  </si>
+  <si>
+    <t>laivənvəntɕietuorxuɑrɕiɑŋpuɕiɑŋ</t>
+  </si>
+  <si>
+    <t>uotsəntimeiiouneipərʂunə</t>
+  </si>
+  <si>
+    <t>nikɑusuŋtʰɑ</t>
+  </si>
+  <si>
+    <t>xɑurxɑurtsoupiepʰɑu</t>
+  </si>
+  <si>
+    <t>ɕiɑuɕinsuɑiɕiɑtɕʰypʰɑpuʂɑŋlai</t>
+  </si>
+  <si>
+    <t>taifutɕiɑunituosueitɕiɑu</t>
+  </si>
+  <si>
+    <t>tsʰouianxɤtʂɤxɤtsʰɑtoupuɕiŋ</t>
+  </si>
+  <si>
+    <t>ianiexɑutsʰɑiexɑuuotoupuɕixuan</t>
+  </si>
+  <si>
+    <t>pukuannitɕʰyputɕʰyfantsəŋuoteitɕʰy</t>
+  </si>
+  <si>
+    <t>uofeitɕʰy</t>
+  </si>
+  <si>
+    <t>nineinianlaiti</t>
+  </si>
+  <si>
+    <t>uosɹ̩tɕʰianniankətɑutipeitɕiŋ</t>
+  </si>
+  <si>
+    <t>tɕiərkəkʰaixueiseisɹ̩tsuɕi</t>
+  </si>
+  <si>
+    <t>niteitɕʰiŋuoituər</t>
+  </si>
+  <si>
+    <t>yetsouyeyanyesuoyetuo</t>
+  </si>
+  <si>
+    <t>pɑneivaniərtikeiuo</t>
+  </si>
+  <si>
+    <t>iouɕietitɕierpɑtʰaiiɑŋtɕiɑuʐɻ̩tʰou</t>
+  </si>
+  <si>
+    <t>niləkueiɕiŋuoɕiŋvɑŋ</t>
+  </si>
+  <si>
+    <t>niɕiŋvɑŋuoieɕiŋvɑŋtsanliɑtouɕiŋvɑŋ</t>
+  </si>
+  <si>
+    <t>nitɕʰiantɕʰypɑuoməntaixuərtsaitɕʰy</t>
+  </si>
+  <si>
+    <t>nitsʰouianmɑ</t>
+  </si>
+  <si>
+    <t>niintipuintineikəʐən</t>
   </si>
 </sst>
 </file>
@@ -3176,10 +4157,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3234,3037 +4215,4027 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:24">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="H2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="J2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="K2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="L2" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="M2" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="N2" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="O2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="P2" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="Q2" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="R2" t="s">
-        <v>881</v>
+        <v>887</v>
+      </c>
+      <c r="S2" t="s">
+        <v>941</v>
+      </c>
+      <c r="T2" t="s">
+        <v>995</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1211</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:24">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="G3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="I3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="J3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="K3" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="L3" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="M3" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="N3" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="O3" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="P3" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="Q3" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="R3" t="s">
-        <v>882</v>
+        <v>888</v>
+      </c>
+      <c r="S3" t="s">
+        <v>942</v>
+      </c>
+      <c r="T3" t="s">
+        <v>996</v>
+      </c>
+      <c r="U3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="V3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="W3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="X3" t="s">
+        <v>1212</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="I4" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="K4" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="L4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="M4" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="N4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="O4" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="P4" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="Q4" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="R4" t="s">
-        <v>883</v>
+        <v>889</v>
+      </c>
+      <c r="S4" t="s">
+        <v>943</v>
+      </c>
+      <c r="T4" t="s">
+        <v>997</v>
+      </c>
+      <c r="U4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="V4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="W4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="X4" t="s">
+        <v>1213</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:24">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G5" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="I5" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="J5" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="K5" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="L5" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="M5" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="N5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="O5" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="P5" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="Q5" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="R5" t="s">
-        <v>884</v>
+        <v>890</v>
+      </c>
+      <c r="S5" t="s">
+        <v>944</v>
+      </c>
+      <c r="T5" t="s">
+        <v>998</v>
+      </c>
+      <c r="U5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="V5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="W5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="X5" t="s">
+        <v>1214</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:24">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F6" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G6" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="I6" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="J6" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="K6" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="L6" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="M6" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="N6" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="O6" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="P6" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="Q6" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="R6" t="s">
-        <v>885</v>
+        <v>891</v>
+      </c>
+      <c r="S6" t="s">
+        <v>945</v>
+      </c>
+      <c r="T6" t="s">
+        <v>999</v>
+      </c>
+      <c r="U6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="V6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="W6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="X6" t="s">
+        <v>1215</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:24">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F7" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G7" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H7" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="I7" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="J7" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="K7" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="L7" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="M7" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="N7" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="O7" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="P7" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="Q7" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="R7" t="s">
-        <v>886</v>
+        <v>892</v>
+      </c>
+      <c r="S7" t="s">
+        <v>946</v>
+      </c>
+      <c r="T7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="U7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="V7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="X7" t="s">
+        <v>1216</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:24">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F8" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="G8" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="H8" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="I8" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="J8" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="K8" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="L8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="M8" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="N8" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="O8" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="P8" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="Q8" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="R8" t="s">
-        <v>887</v>
+        <v>893</v>
+      </c>
+      <c r="S8" t="s">
+        <v>947</v>
+      </c>
+      <c r="T8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="U8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="V8" t="s">
+        <v>1109</v>
+      </c>
+      <c r="W8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="X8" t="s">
+        <v>1217</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:24">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="G9" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="H9" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I9" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="J9" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="K9" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="L9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="M9" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="N9" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="O9" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="P9" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="Q9" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="R9" t="s">
-        <v>888</v>
+        <v>894</v>
+      </c>
+      <c r="S9" t="s">
+        <v>948</v>
+      </c>
+      <c r="T9" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U9" t="s">
+        <v>1056</v>
+      </c>
+      <c r="V9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="W9" t="s">
+        <v>1164</v>
+      </c>
+      <c r="X9" t="s">
+        <v>1218</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:24">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="H10" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="I10" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="J10" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="K10" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="L10" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="M10" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="N10" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="O10" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="P10" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="Q10" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="R10" t="s">
-        <v>889</v>
+        <v>895</v>
+      </c>
+      <c r="S10" t="s">
+        <v>949</v>
+      </c>
+      <c r="T10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="U10" t="s">
+        <v>1057</v>
+      </c>
+      <c r="V10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="W10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="X10" t="s">
+        <v>1219</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:24">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F11" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G11" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H11" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="I11" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="J11" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="K11" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="L11" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="M11" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="N11" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="O11" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="P11" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="Q11" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="R11" t="s">
-        <v>890</v>
+        <v>896</v>
+      </c>
+      <c r="S11" t="s">
+        <v>950</v>
+      </c>
+      <c r="T11" t="s">
+        <v>1004</v>
+      </c>
+      <c r="U11" t="s">
+        <v>1058</v>
+      </c>
+      <c r="V11" t="s">
+        <v>1112</v>
+      </c>
+      <c r="W11" t="s">
+        <v>1166</v>
+      </c>
+      <c r="X11" t="s">
+        <v>1220</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:24">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F12" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="G12" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="H12" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I12" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="J12" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="K12" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="L12" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="M12" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="N12" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="O12" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="P12" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="R12" t="s">
-        <v>891</v>
+        <v>897</v>
+      </c>
+      <c r="S12" t="s">
+        <v>951</v>
+      </c>
+      <c r="T12" t="s">
+        <v>1005</v>
+      </c>
+      <c r="U12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="V12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="W12" t="s">
+        <v>1167</v>
+      </c>
+      <c r="X12" t="s">
+        <v>1221</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:24">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F13" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G13" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H13" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="I13" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="J13" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="L13" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="M13" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="N13" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="O13" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="P13" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="Q13" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="R13" t="s">
-        <v>892</v>
+        <v>898</v>
+      </c>
+      <c r="S13" t="s">
+        <v>952</v>
+      </c>
+      <c r="T13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="U13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="V13" t="s">
+        <v>1114</v>
+      </c>
+      <c r="W13" t="s">
+        <v>1168</v>
+      </c>
+      <c r="X13" t="s">
+        <v>1222</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:24">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:24">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F15" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="G15" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H15" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="I15" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="J15" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="K15" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L15" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="M15" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="N15" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="O15" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="P15" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="Q15" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="R15" t="s">
-        <v>893</v>
+        <v>899</v>
+      </c>
+      <c r="S15" t="s">
+        <v>953</v>
+      </c>
+      <c r="T15" t="s">
+        <v>1007</v>
+      </c>
+      <c r="U15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="V15" t="s">
+        <v>1115</v>
+      </c>
+      <c r="W15" t="s">
+        <v>1169</v>
+      </c>
+      <c r="X15" t="s">
+        <v>1223</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:24">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F16" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G16" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H16" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="I16" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="J16" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="K16" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L16" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M16" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="N16" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="O16" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="P16" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="Q16" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="R16" t="s">
-        <v>894</v>
+        <v>900</v>
+      </c>
+      <c r="S16" t="s">
+        <v>954</v>
+      </c>
+      <c r="T16" t="s">
+        <v>1008</v>
+      </c>
+      <c r="U16" t="s">
+        <v>1062</v>
+      </c>
+      <c r="V16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="W16" t="s">
+        <v>1170</v>
+      </c>
+      <c r="X16" t="s">
+        <v>1224</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F17" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="G17" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H17" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="I17" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="J17" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="K17" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="L17" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="M17" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="N17" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="O17" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="P17" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="Q17" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="R17" t="s">
-        <v>895</v>
+        <v>901</v>
+      </c>
+      <c r="S17" t="s">
+        <v>955</v>
+      </c>
+      <c r="T17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="U17" t="s">
+        <v>1063</v>
+      </c>
+      <c r="V17" t="s">
+        <v>1117</v>
+      </c>
+      <c r="W17" t="s">
+        <v>1171</v>
+      </c>
+      <c r="X17" t="s">
+        <v>1225</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F18" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G18" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="H18" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="J18" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="K18" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L18" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="M18" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="N18" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="O18" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="P18" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="Q18" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="R18" t="s">
-        <v>896</v>
+        <v>902</v>
+      </c>
+      <c r="S18" t="s">
+        <v>956</v>
+      </c>
+      <c r="T18" t="s">
+        <v>1010</v>
+      </c>
+      <c r="U18" t="s">
+        <v>1064</v>
+      </c>
+      <c r="V18" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W18" t="s">
+        <v>1172</v>
+      </c>
+      <c r="X18" t="s">
+        <v>1226</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F19" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="G19" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="H19" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="I19" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J19" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K19" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="L19" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="M19" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="N19" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="O19" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="P19" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="Q19" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="R19" t="s">
-        <v>897</v>
+        <v>903</v>
+      </c>
+      <c r="S19" t="s">
+        <v>957</v>
+      </c>
+      <c r="T19" t="s">
+        <v>1011</v>
+      </c>
+      <c r="U19" t="s">
+        <v>1065</v>
+      </c>
+      <c r="V19" t="s">
+        <v>1119</v>
+      </c>
+      <c r="W19" t="s">
+        <v>1173</v>
+      </c>
+      <c r="X19" t="s">
+        <v>1227</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F20" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G20" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H20" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="I20" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="J20" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="K20" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="L20" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="M20" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="N20" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="O20" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="P20" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="Q20" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="R20" t="s">
-        <v>898</v>
+        <v>904</v>
+      </c>
+      <c r="S20" t="s">
+        <v>958</v>
+      </c>
+      <c r="T20" t="s">
+        <v>1012</v>
+      </c>
+      <c r="U20" t="s">
+        <v>1066</v>
+      </c>
+      <c r="V20" t="s">
+        <v>1120</v>
+      </c>
+      <c r="W20" t="s">
+        <v>1174</v>
+      </c>
+      <c r="X20" t="s">
+        <v>1228</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F21" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G21" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H21" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="I21" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="J21" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="K21" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="L21" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="M21" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="N21" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="O21" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="P21" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="Q21" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="R21" t="s">
-        <v>899</v>
+        <v>905</v>
+      </c>
+      <c r="S21" t="s">
+        <v>959</v>
+      </c>
+      <c r="T21" t="s">
+        <v>1013</v>
+      </c>
+      <c r="U21" t="s">
+        <v>1067</v>
+      </c>
+      <c r="V21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="W21" t="s">
+        <v>1175</v>
+      </c>
+      <c r="X21" t="s">
+        <v>1229</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:24">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E22" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F22" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G22" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="H22" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="I22" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="J22" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="K22" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="L22" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="M22" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="N22" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="O22" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="P22" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="Q22" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="R22" t="s">
-        <v>900</v>
+        <v>906</v>
+      </c>
+      <c r="S22" t="s">
+        <v>960</v>
+      </c>
+      <c r="T22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="U22" t="s">
+        <v>1068</v>
+      </c>
+      <c r="V22" t="s">
+        <v>1122</v>
+      </c>
+      <c r="W22" t="s">
+        <v>1176</v>
+      </c>
+      <c r="X22" t="s">
+        <v>1230</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:24">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F23" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G23" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="H23" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="I23" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="J23" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="K23" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="L23" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="M23" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="N23" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="O23" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="P23" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="Q23" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="R23" t="s">
-        <v>901</v>
+        <v>907</v>
+      </c>
+      <c r="S23" t="s">
+        <v>961</v>
+      </c>
+      <c r="T23" t="s">
+        <v>1015</v>
+      </c>
+      <c r="U23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="V23" t="s">
+        <v>1123</v>
+      </c>
+      <c r="W23" t="s">
+        <v>1177</v>
+      </c>
+      <c r="X23" t="s">
+        <v>1231</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:24">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E24" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F24" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G24" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="H24" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="I24" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="J24" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="K24" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="L24" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="M24" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="N24" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="O24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="P24" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="Q24" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="R24" t="s">
-        <v>902</v>
+        <v>908</v>
+      </c>
+      <c r="S24" t="s">
+        <v>962</v>
+      </c>
+      <c r="T24" t="s">
+        <v>1016</v>
+      </c>
+      <c r="U24" t="s">
+        <v>1070</v>
+      </c>
+      <c r="V24" t="s">
+        <v>1124</v>
+      </c>
+      <c r="W24" t="s">
+        <v>1178</v>
+      </c>
+      <c r="X24" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:24">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F25" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="G25" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H25" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="I25" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="J25" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="K25" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="L25" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="M25" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="N25" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="O25" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="P25" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="Q25" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="R25" t="s">
-        <v>903</v>
+        <v>909</v>
+      </c>
+      <c r="S25" t="s">
+        <v>963</v>
+      </c>
+      <c r="T25" t="s">
+        <v>1017</v>
+      </c>
+      <c r="U25" t="s">
+        <v>1071</v>
+      </c>
+      <c r="V25" t="s">
+        <v>1125</v>
+      </c>
+      <c r="W25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="X25" t="s">
+        <v>1232</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:24">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F26" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="G26" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H26" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="I26" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="J26" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K26" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="L26" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="M26" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="N26" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="O26" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="P26" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="Q26" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="R26" t="s">
-        <v>904</v>
+        <v>910</v>
+      </c>
+      <c r="S26" t="s">
+        <v>964</v>
+      </c>
+      <c r="T26" t="s">
+        <v>1018</v>
+      </c>
+      <c r="U26" t="s">
+        <v>1072</v>
+      </c>
+      <c r="V26" t="s">
+        <v>1126</v>
+      </c>
+      <c r="W26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="X26" t="s">
+        <v>1233</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:24">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F27" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G27" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H27" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="I27" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="J27" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="K27" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="L27" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="M27" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="N27" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="O27" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="P27" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="Q27" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="R27" t="s">
-        <v>905</v>
+        <v>911</v>
+      </c>
+      <c r="S27" t="s">
+        <v>965</v>
+      </c>
+      <c r="T27" t="s">
+        <v>1019</v>
+      </c>
+      <c r="U27" t="s">
+        <v>1073</v>
+      </c>
+      <c r="V27" t="s">
+        <v>1127</v>
+      </c>
+      <c r="W27" t="s">
+        <v>1181</v>
+      </c>
+      <c r="X27" t="s">
+        <v>1234</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:24">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E28" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F28" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G28" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="H28" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="I28" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="J28" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="K28" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="L28" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="M28" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="N28" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="O28" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="P28" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="Q28" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="R28" t="s">
-        <v>906</v>
+        <v>912</v>
+      </c>
+      <c r="S28" t="s">
+        <v>966</v>
+      </c>
+      <c r="T28" t="s">
+        <v>1020</v>
+      </c>
+      <c r="U28" t="s">
+        <v>1074</v>
+      </c>
+      <c r="V28" t="s">
+        <v>1128</v>
+      </c>
+      <c r="W28" t="s">
+        <v>1182</v>
+      </c>
+      <c r="X28" t="s">
+        <v>1235</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:24">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F29" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="G29" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H29" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="I29" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="J29" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="K29" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L29" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="M29" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="N29" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="O29" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="P29" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="Q29" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="R29" t="s">
-        <v>907</v>
+        <v>913</v>
+      </c>
+      <c r="S29" t="s">
+        <v>967</v>
+      </c>
+      <c r="T29" t="s">
+        <v>1021</v>
+      </c>
+      <c r="U29" t="s">
+        <v>1075</v>
+      </c>
+      <c r="V29" t="s">
+        <v>1129</v>
+      </c>
+      <c r="W29" t="s">
+        <v>1183</v>
+      </c>
+      <c r="X29" t="s">
+        <v>1236</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:24">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F30" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G30" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="H30" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="I30" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="J30" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="K30" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L30" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="M30" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="N30" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="O30" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="P30" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="Q30" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="R30" t="s">
-        <v>908</v>
+        <v>914</v>
+      </c>
+      <c r="S30" t="s">
+        <v>968</v>
+      </c>
+      <c r="T30" t="s">
+        <v>1022</v>
+      </c>
+      <c r="U30" t="s">
+        <v>1076</v>
+      </c>
+      <c r="V30" t="s">
+        <v>1130</v>
+      </c>
+      <c r="W30" t="s">
+        <v>1184</v>
+      </c>
+      <c r="X30" t="s">
+        <v>1237</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:24">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E31" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F31" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G31" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H31" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="I31" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="J31" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="K31" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="L31" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="M31" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="N31" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="O31" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="P31" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="Q31" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="R31" t="s">
-        <v>909</v>
+        <v>915</v>
+      </c>
+      <c r="S31" t="s">
+        <v>969</v>
+      </c>
+      <c r="T31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="U31" t="s">
+        <v>1077</v>
+      </c>
+      <c r="V31" t="s">
+        <v>1131</v>
+      </c>
+      <c r="W31" t="s">
+        <v>1185</v>
+      </c>
+      <c r="X31" t="s">
+        <v>1238</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:24">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E32" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F32" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G32" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="H32" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="I32" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="J32" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="K32" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="L32" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M32" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="N32" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="O32" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="P32" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="Q32" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="R32" t="s">
-        <v>910</v>
+        <v>916</v>
+      </c>
+      <c r="S32" t="s">
+        <v>970</v>
+      </c>
+      <c r="T32" t="s">
+        <v>1024</v>
+      </c>
+      <c r="U32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="V32" t="s">
+        <v>1132</v>
+      </c>
+      <c r="W32" t="s">
+        <v>1186</v>
+      </c>
+      <c r="X32" t="s">
+        <v>1239</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:24">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E33" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F33" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G33" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="H33" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="I33" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J33" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="K33" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="L33" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="M33" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="N33" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="O33" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="P33" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="Q33" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="R33" t="s">
-        <v>911</v>
+        <v>917</v>
+      </c>
+      <c r="S33" t="s">
+        <v>971</v>
+      </c>
+      <c r="T33" t="s">
+        <v>1025</v>
+      </c>
+      <c r="U33" t="s">
+        <v>1079</v>
+      </c>
+      <c r="V33" t="s">
+        <v>1133</v>
+      </c>
+      <c r="W33" t="s">
+        <v>1187</v>
+      </c>
+      <c r="X33" t="s">
+        <v>1240</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:24">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E34" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F34" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G34" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H34" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="I34" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="J34" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="K34" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="L34" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="M34" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="N34" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="O34" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="P34" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="Q34" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="R34" t="s">
-        <v>912</v>
+        <v>918</v>
+      </c>
+      <c r="S34" t="s">
+        <v>972</v>
+      </c>
+      <c r="T34" t="s">
+        <v>1026</v>
+      </c>
+      <c r="U34" t="s">
+        <v>1080</v>
+      </c>
+      <c r="V34" t="s">
+        <v>1134</v>
+      </c>
+      <c r="W34" t="s">
+        <v>1188</v>
+      </c>
+      <c r="X34" t="s">
+        <v>756</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:24">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E35" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F35" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G35" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="H35" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="I35" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="J35" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="K35" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="L35" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="M35" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="N35" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="O35" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="P35" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="Q35" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="R35" t="s">
-        <v>913</v>
+        <v>919</v>
+      </c>
+      <c r="S35" t="s">
+        <v>973</v>
+      </c>
+      <c r="T35" t="s">
+        <v>1027</v>
+      </c>
+      <c r="U35" t="s">
+        <v>1081</v>
+      </c>
+      <c r="V35" t="s">
+        <v>1135</v>
+      </c>
+      <c r="W35" t="s">
+        <v>1189</v>
+      </c>
+      <c r="X35" t="s">
+        <v>1241</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:24">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F36" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G36" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="H36" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I36" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="J36" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="K36" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="L36" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="M36" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="N36" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="O36" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="P36" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="Q36" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="R36" t="s">
-        <v>914</v>
+        <v>920</v>
+      </c>
+      <c r="S36" t="s">
+        <v>974</v>
+      </c>
+      <c r="T36" t="s">
+        <v>1028</v>
+      </c>
+      <c r="U36" t="s">
+        <v>1082</v>
+      </c>
+      <c r="V36" t="s">
+        <v>1136</v>
+      </c>
+      <c r="W36" t="s">
+        <v>1190</v>
+      </c>
+      <c r="X36" t="s">
+        <v>1242</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:24">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E37" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F37" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G37" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="H37" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="I37" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="J37" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="K37" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="L37" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="M37" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="N37" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="O37" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="P37" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="Q37" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="R37" t="s">
-        <v>915</v>
+        <v>921</v>
+      </c>
+      <c r="S37" t="s">
+        <v>975</v>
+      </c>
+      <c r="T37" t="s">
+        <v>1029</v>
+      </c>
+      <c r="U37" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V37" t="s">
+        <v>1137</v>
+      </c>
+      <c r="W37" t="s">
+        <v>1191</v>
+      </c>
+      <c r="X37" t="s">
+        <v>1243</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:24">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F38" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G38" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="H38" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="I38" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="J38" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="K38" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="L38" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="M38" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="N38" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="O38" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="P38" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="Q38" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="R38" t="s">
-        <v>916</v>
+        <v>922</v>
+      </c>
+      <c r="S38" t="s">
+        <v>976</v>
+      </c>
+      <c r="T38" t="s">
+        <v>1030</v>
+      </c>
+      <c r="U38" t="s">
+        <v>1084</v>
+      </c>
+      <c r="V38" t="s">
+        <v>1138</v>
+      </c>
+      <c r="W38" t="s">
+        <v>1192</v>
+      </c>
+      <c r="X38" t="s">
+        <v>1244</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:24">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F39" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="G39" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="H39" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="I39" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="J39" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="K39" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="L39" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="M39" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="N39" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="O39" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="P39" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="Q39" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="R39" t="s">
-        <v>917</v>
+        <v>923</v>
+      </c>
+      <c r="S39" t="s">
+        <v>977</v>
+      </c>
+      <c r="T39" t="s">
+        <v>1031</v>
+      </c>
+      <c r="U39" t="s">
+        <v>1085</v>
+      </c>
+      <c r="V39" t="s">
+        <v>1139</v>
+      </c>
+      <c r="W39" t="s">
+        <v>1193</v>
+      </c>
+      <c r="X39" t="s">
+        <v>1245</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:24">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E40" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F40" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="G40" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="H40" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="I40" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="J40" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="K40" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="L40" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="M40" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="N40" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="O40" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="P40" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="Q40" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="R40" t="s">
-        <v>918</v>
+        <v>924</v>
+      </c>
+      <c r="S40" t="s">
+        <v>978</v>
+      </c>
+      <c r="T40" t="s">
+        <v>1032</v>
+      </c>
+      <c r="U40" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V40" t="s">
+        <v>1140</v>
+      </c>
+      <c r="W40" t="s">
+        <v>1194</v>
+      </c>
+      <c r="X40" t="s">
+        <v>1246</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:24">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E41" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F41" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="G41" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="H41" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="I41" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="J41" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="K41" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="L41" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="M41" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="N41" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="O41" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="P41" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="Q41" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="R41" t="s">
-        <v>919</v>
+        <v>925</v>
+      </c>
+      <c r="S41" t="s">
+        <v>979</v>
+      </c>
+      <c r="T41" t="s">
+        <v>1033</v>
+      </c>
+      <c r="U41" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V41" t="s">
+        <v>1141</v>
+      </c>
+      <c r="W41" t="s">
+        <v>1195</v>
+      </c>
+      <c r="X41" t="s">
+        <v>1247</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:24">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E42" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F42" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="G42" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="H42" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="I42" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="J42" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="K42" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="L42" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="M42" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="N42" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="O42" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="P42" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="Q42" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="R42" t="s">
-        <v>920</v>
+        <v>926</v>
+      </c>
+      <c r="S42" t="s">
+        <v>980</v>
+      </c>
+      <c r="T42" t="s">
+        <v>1034</v>
+      </c>
+      <c r="U42" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V42" t="s">
+        <v>1142</v>
+      </c>
+      <c r="W42" t="s">
+        <v>1196</v>
+      </c>
+      <c r="X42" t="s">
+        <v>1248</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:24">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F43" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G43" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="H43" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I43" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="J43" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="K43" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="L43" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="M43" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="N43" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="O43" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="P43" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="Q43" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="R43" t="s">
-        <v>921</v>
+        <v>927</v>
+      </c>
+      <c r="S43" t="s">
+        <v>981</v>
+      </c>
+      <c r="T43" t="s">
+        <v>1035</v>
+      </c>
+      <c r="U43" t="s">
+        <v>1089</v>
+      </c>
+      <c r="V43" t="s">
+        <v>1143</v>
+      </c>
+      <c r="W43" t="s">
+        <v>1197</v>
+      </c>
+      <c r="X43" t="s">
+        <v>1249</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:24">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E44" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F44" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G44" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H44" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I44" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="J44" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="K44" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="L44" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="M44" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="N44" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="O44" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="P44" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="Q44" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="R44" t="s">
-        <v>922</v>
+        <v>928</v>
+      </c>
+      <c r="S44" t="s">
+        <v>982</v>
+      </c>
+      <c r="T44" t="s">
+        <v>1036</v>
+      </c>
+      <c r="U44" t="s">
+        <v>1090</v>
+      </c>
+      <c r="V44" t="s">
+        <v>1144</v>
+      </c>
+      <c r="W44" t="s">
+        <v>1198</v>
+      </c>
+      <c r="X44" t="s">
+        <v>1250</v>
       </c>
     </row>
-    <row r="45" spans="1:18">
+    <row r="45" spans="1:24">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D45" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E45" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F45" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="G45" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="H45" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="I45" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="J45" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="K45" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="L45" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="M45" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="N45" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="O45" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="P45" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="Q45" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="R45" t="s">
-        <v>923</v>
+        <v>929</v>
+      </c>
+      <c r="S45" t="s">
+        <v>983</v>
+      </c>
+      <c r="T45" t="s">
+        <v>1037</v>
+      </c>
+      <c r="U45" t="s">
+        <v>1091</v>
+      </c>
+      <c r="V45" t="s">
+        <v>1145</v>
+      </c>
+      <c r="W45" t="s">
+        <v>1199</v>
+      </c>
+      <c r="X45" t="s">
+        <v>1251</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:24">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D46" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F46" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="G46" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H46" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I46" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="J46" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="K46" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="L46" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="M46" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="N46" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="O46" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="P46" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="Q46" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="R46" t="s">
-        <v>924</v>
+        <v>930</v>
+      </c>
+      <c r="S46" t="s">
+        <v>984</v>
+      </c>
+      <c r="T46" t="s">
+        <v>1038</v>
+      </c>
+      <c r="U46" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V46" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W46" t="s">
+        <v>1200</v>
+      </c>
+      <c r="X46" t="s">
+        <v>1252</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:24">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D47" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F47" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G47" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="H47" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="I47" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J47" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="K47" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="L47" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="M47" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="N47" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="O47" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="P47" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="Q47" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="R47" t="s">
-        <v>925</v>
+        <v>931</v>
+      </c>
+      <c r="S47" t="s">
+        <v>985</v>
+      </c>
+      <c r="T47" t="s">
+        <v>1039</v>
+      </c>
+      <c r="U47" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V47" t="s">
+        <v>1147</v>
+      </c>
+      <c r="W47" t="s">
+        <v>1201</v>
+      </c>
+      <c r="X47" t="s">
+        <v>1253</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
+    <row r="48" spans="1:24">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D48" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E48" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F48" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G48" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="H48" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="I48" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="J48" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="K48" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="L48" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="M48" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="N48" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="O48" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="P48" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="Q48" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="R48" t="s">
-        <v>926</v>
+        <v>932</v>
+      </c>
+      <c r="S48" t="s">
+        <v>986</v>
+      </c>
+      <c r="T48" t="s">
+        <v>1040</v>
+      </c>
+      <c r="U48" t="s">
+        <v>1094</v>
+      </c>
+      <c r="V48" t="s">
+        <v>1148</v>
+      </c>
+      <c r="W48" t="s">
+        <v>1202</v>
+      </c>
+      <c r="X48" t="s">
+        <v>770</v>
       </c>
     </row>
-    <row r="49" spans="1:18">
+    <row r="49" spans="1:24">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D49" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F49" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G49" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="H49" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="I49" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="J49" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="K49" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="L49" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="M49" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="N49" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="O49" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="P49" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="Q49" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="R49" t="s">
-        <v>927</v>
+        <v>933</v>
+      </c>
+      <c r="S49" t="s">
+        <v>987</v>
+      </c>
+      <c r="T49" t="s">
+        <v>1041</v>
+      </c>
+      <c r="U49" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V49" t="s">
+        <v>1149</v>
+      </c>
+      <c r="W49" t="s">
+        <v>1203</v>
+      </c>
+      <c r="X49" t="s">
+        <v>1254</v>
       </c>
     </row>
-    <row r="50" spans="1:18">
+    <row r="50" spans="1:24">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D50" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E50" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G50" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="H50" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="I50" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="J50" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="K50" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="L50" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="M50" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="N50" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="O50" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="P50" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="Q50" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="R50" t="s">
-        <v>928</v>
+        <v>934</v>
+      </c>
+      <c r="S50" t="s">
+        <v>988</v>
+      </c>
+      <c r="T50" t="s">
+        <v>1042</v>
+      </c>
+      <c r="U50" t="s">
+        <v>1096</v>
+      </c>
+      <c r="V50" t="s">
+        <v>1150</v>
+      </c>
+      <c r="W50" t="s">
+        <v>1204</v>
+      </c>
+      <c r="X50" t="s">
+        <v>1255</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:24">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D51" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E51" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F51" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G51" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="H51" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I51" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="J51" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="K51" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="L51" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="M51" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="N51" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="O51" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="P51" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="Q51" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="R51" t="s">
-        <v>929</v>
+        <v>935</v>
+      </c>
+      <c r="S51" t="s">
+        <v>989</v>
+      </c>
+      <c r="T51" t="s">
+        <v>1043</v>
+      </c>
+      <c r="U51" t="s">
+        <v>1097</v>
+      </c>
+      <c r="V51" t="s">
+        <v>1151</v>
+      </c>
+      <c r="W51" t="s">
+        <v>1205</v>
+      </c>
+      <c r="X51" t="s">
+        <v>1256</v>
       </c>
     </row>
-    <row r="52" spans="1:18">
+    <row r="52" spans="1:24">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D52" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E52" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F52" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G52" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="H52" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="I52" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="J52" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K52" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="L52" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="M52" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="N52" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="O52" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="P52" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="Q52" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="R52" t="s">
-        <v>930</v>
+        <v>936</v>
+      </c>
+      <c r="S52" t="s">
+        <v>990</v>
+      </c>
+      <c r="T52" t="s">
+        <v>1044</v>
+      </c>
+      <c r="U52" t="s">
+        <v>1098</v>
+      </c>
+      <c r="V52" t="s">
+        <v>1152</v>
+      </c>
+      <c r="W52" t="s">
+        <v>1206</v>
+      </c>
+      <c r="X52" t="s">
+        <v>1257</v>
       </c>
     </row>
-    <row r="53" spans="1:18">
+    <row r="53" spans="1:24">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F53" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G53" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="H53" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="I53" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="J53" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="K53" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="L53" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M53" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="N53" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="O53" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="P53" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="Q53" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="R53" t="s">
-        <v>931</v>
+        <v>937</v>
+      </c>
+      <c r="S53" t="s">
+        <v>991</v>
+      </c>
+      <c r="T53" t="s">
+        <v>1045</v>
+      </c>
+      <c r="U53" t="s">
+        <v>1099</v>
+      </c>
+      <c r="V53" t="s">
+        <v>1153</v>
+      </c>
+      <c r="W53" t="s">
+        <v>1207</v>
+      </c>
+      <c r="X53" t="s">
+        <v>1258</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
+    <row r="54" spans="1:24">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D54" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E54" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F54" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="G54" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H54" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="I54" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="J54" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="K54" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L54" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="M54" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="N54" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="O54" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="P54" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="Q54" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="R54" t="s">
-        <v>932</v>
+        <v>938</v>
+      </c>
+      <c r="S54" t="s">
+        <v>992</v>
+      </c>
+      <c r="T54" t="s">
+        <v>1046</v>
+      </c>
+      <c r="U54" t="s">
+        <v>1100</v>
+      </c>
+      <c r="V54" t="s">
+        <v>1154</v>
+      </c>
+      <c r="W54" t="s">
+        <v>1208</v>
+      </c>
+      <c r="X54" t="s">
+        <v>1259</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:24">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D55" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F55" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G55" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="H55" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="I55" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="J55" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="K55" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="L55" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="M55" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="N55" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="O55" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="P55" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="Q55" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="R55" t="s">
-        <v>933</v>
+        <v>939</v>
+      </c>
+      <c r="S55" t="s">
+        <v>993</v>
+      </c>
+      <c r="T55" t="s">
+        <v>1047</v>
+      </c>
+      <c r="U55" t="s">
+        <v>1101</v>
+      </c>
+      <c r="V55" t="s">
+        <v>1155</v>
+      </c>
+      <c r="W55" t="s">
+        <v>1209</v>
+      </c>
+      <c r="X55" t="s">
+        <v>1260</v>
       </c>
     </row>
-    <row r="56" spans="1:18">
+    <row r="56" spans="1:24">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D56" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F56" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G56" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="H56" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="I56" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="J56" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="K56" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="L56" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="M56" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="N56" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="O56" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="P56" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="Q56" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="R56" t="s">
-        <v>934</v>
+        <v>940</v>
+      </c>
+      <c r="S56" t="s">
+        <v>994</v>
+      </c>
+      <c r="T56" t="s">
+        <v>1048</v>
+      </c>
+      <c r="U56" t="s">
+        <v>1102</v>
+      </c>
+      <c r="V56" t="s">
+        <v>1156</v>
+      </c>
+      <c r="W56" t="s">
+        <v>1210</v>
+      </c>
+      <c r="X56" t="s">
+        <v>1261</v>
       </c>
     </row>
   </sheetData>
